--- a/排阵/对阵表.xlsx
+++ b/排阵/对阵表.xlsx
@@ -478,21 +478,21 @@
     <col width="22" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
+    <row r="1" ht="27" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>科技球队日常训练活动 - 对阵表（2026年04月13日）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="32" customHeight="1">
+          <t>科技球队日常训练活动 - 对阵表（2026年07月06日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="27" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>场地数：3个 | 时长：2 小时 | 赛制：15 分/局，2 局 | 项目：男双、女双、混双</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="32" customHeight="1">
+    <row r="3" ht="27" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>轮次</t>
@@ -529,7 +529,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="32" customHeight="1">
+    <row r="4" ht="27" customHeight="1">
       <c r="A4" s="4" t="n">
         <v>1</v>
       </c>
@@ -545,18 +545,18 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>李祺祺/田茜</t>
+          <t>滕菲/唐英武</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr"/>
       <c r="F4" s="4" t="inlineStr"/>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>滕菲/崔倩男</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="32" customHeight="1">
+          <t>李祺祺/张燕红</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="27" customHeight="1">
       <c r="A5" s="4" t="n">
         <v>1</v>
       </c>
@@ -572,18 +572,18 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>严勇文/卢志辉</t>
+          <t>罗琴荩/苏大哲</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr"/>
       <c r="F5" s="4" t="inlineStr"/>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>罗蒙/陈顺星</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="32" customHeight="1">
+          <t>严勇文/陈财贵</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="27" customHeight="1">
       <c r="A6" s="4" t="n">
         <v>1</v>
       </c>
@@ -599,18 +599,18 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>林锋/罗琴荩</t>
+          <t>陈小洪/董广博</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr"/>
       <c r="F6" s="4" t="inlineStr"/>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>苏大哲/刘继宇</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="32" customHeight="1">
+          <t>刘继宇/王小波</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="27" customHeight="1">
       <c r="A7" s="4" t="n">
         <v>2</v>
       </c>
@@ -626,18 +626,18 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>李祺祺/崔倩男</t>
+          <t>李祺祺/张燕红</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr"/>
       <c r="F7" s="4" t="inlineStr"/>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>滕菲/田茜</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="32" customHeight="1">
+          <t>滕菲/唐英武</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="27" customHeight="1">
       <c r="A8" s="4" t="n">
         <v>2</v>
       </c>
@@ -653,18 +653,18 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>严勇文/黄冬青</t>
+          <t>张欣欣/卢志辉</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr"/>
       <c r="F8" s="4" t="inlineStr"/>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>陈小洪/王小波</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="32" customHeight="1">
+          <t>严勇文/黄冬青</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="27" customHeight="1">
       <c r="A9" s="4" t="n">
         <v>2</v>
       </c>
@@ -680,18 +680,18 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>林锋/罗琴荩</t>
+          <t>刘继宇/程建兴</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr"/>
       <c r="F9" s="4" t="inlineStr"/>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>陈顺星/苏大哲</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="32" customHeight="1">
+          <t>王小波/罗琴荩</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="27" customHeight="1">
       <c r="A10" s="4" t="n">
         <v>3</v>
       </c>
@@ -707,18 +707,18 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>崔倩男/田茜</t>
+          <t>张燕红/唐英武</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr"/>
       <c r="F10" s="4" t="inlineStr"/>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>李祺祺/滕菲</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="32" customHeight="1">
+          <t>滕菲/李祺祺</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="27" customHeight="1">
       <c r="A11" s="4" t="n">
         <v>3</v>
       </c>
@@ -734,18 +734,18 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>严勇文/卢志辉</t>
+          <t>陈小洪/苏大哲</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr"/>
       <c r="F11" s="4" t="inlineStr"/>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>刘继宇/王小波</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="32" customHeight="1">
+          <t>严勇文/卢志辉</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="27" customHeight="1">
       <c r="A12" s="4" t="n">
         <v>3</v>
       </c>
@@ -761,18 +761,18 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>罗蒙/黄冬青</t>
+          <t>董广博/程建兴</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr"/>
       <c r="F12" s="4" t="inlineStr"/>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>陈顺星/陈小洪</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="32" customHeight="1">
+          <t>陈财贵/黄冬青</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="27" customHeight="1">
       <c r="A13" s="4" t="n">
         <v>4</v>
       </c>
@@ -788,18 +788,18 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>滕菲/田茜</t>
+          <t>滕菲/李祺祺</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr"/>
       <c r="F13" s="4" t="inlineStr"/>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>李祺祺/崔倩男</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="32" customHeight="1">
+          <t>张燕红/唐英武</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="27" customHeight="1">
       <c r="A14" s="4" t="n">
         <v>4</v>
       </c>
@@ -815,18 +815,18 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>严勇文/罗蒙</t>
+          <t>罗琴荩/苏大哲</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr"/>
       <c r="F14" s="4" t="inlineStr"/>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>苏大哲/刘继宇</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="32" customHeight="1">
+          <t>严勇文/张欣欣</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="27" customHeight="1">
       <c r="A15" s="4" t="n">
         <v>4</v>
       </c>
@@ -842,18 +842,18 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>林锋/罗琴荩</t>
+          <t>王小波/陈小洪</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr"/>
       <c r="F15" s="4" t="inlineStr"/>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>陈小洪/王小波</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="32" customHeight="1">
+          <t>刘继宇/陈财贵</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="27" customHeight="1">
       <c r="A16" s="4" t="n">
         <v>5</v>
       </c>
@@ -864,23 +864,23 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>混双</t>
+          <t>男双</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>陈顺星/李祺祺</t>
+          <t>严勇文/黄冬青</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr"/>
       <c r="F16" s="4" t="inlineStr"/>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>王小波/崔倩男</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="32" customHeight="1">
+          <t>卢志辉/董广博</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="27" customHeight="1">
       <c r="A17" s="4" t="n">
         <v>5</v>
       </c>
@@ -891,23 +891,23 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>混双</t>
+          <t>男双</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>林锋/滕菲</t>
+          <t>罗琴荩/张欣欣</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr"/>
       <c r="F17" s="4" t="inlineStr"/>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>罗琴荩/田茜</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="32" customHeight="1">
+          <t>陈财贵/程建兴</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="27" customHeight="1">
       <c r="A18" s="4" t="n">
         <v>5</v>
       </c>
@@ -923,18 +923,18 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>严勇文/黄冬青</t>
+          <t>王小波/苏大哲</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr"/>
       <c r="F18" s="4" t="inlineStr"/>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>罗蒙/卢志辉</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="32" customHeight="1">
+          <t>刘继宇/陈小洪</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="27" customHeight="1">
       <c r="A19" s="4" t="n">
         <v>6</v>
       </c>
@@ -945,23 +945,23 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>混双</t>
+          <t>男双</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>罗蒙/李祺祺</t>
+          <t>卢志辉/程建兴</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr"/>
       <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>陈顺星/田茜</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="32" customHeight="1">
+          <t>黄冬青/董广博</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="27" customHeight="1">
       <c r="A20" s="4" t="n">
         <v>6</v>
       </c>
@@ -977,18 +977,18 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>苏大哲/陈小洪</t>
+          <t>罗琴荩/张欣欣</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr"/>
       <c r="F20" s="4" t="inlineStr"/>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>刘继宇/卢志辉</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="32" customHeight="1">
+          <t>刘继宇/陈财贵</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="27" customHeight="1">
       <c r="A21" s="4" t="n">
         <v>6</v>
       </c>
@@ -999,23 +999,23 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>男双</t>
+          <t>女双</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>罗琴荩/黄冬青</t>
+          <t>滕菲/张燕红</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr"/>
       <c r="F21" s="4" t="inlineStr"/>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>林锋/王小波</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="32" customHeight="1">
+          <t>李祺祺/唐英武</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="27" customHeight="1">
       <c r="A22" s="4" t="n">
         <v>7</v>
       </c>
@@ -1026,23 +1026,23 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>混双</t>
+          <t>女双</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>罗蒙/李祺祺</t>
+          <t>李祺祺/唐英武</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr"/>
       <c r="F22" s="4" t="inlineStr"/>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>林锋/滕菲</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="32" customHeight="1">
+          <t>滕菲/张燕红</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="27" customHeight="1">
       <c r="A23" s="4" t="n">
         <v>7</v>
       </c>
@@ -1058,18 +1058,18 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>苏大哲/刘继宇</t>
+          <t>苏大哲/卢志辉</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr"/>
       <c r="F23" s="4" t="inlineStr"/>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>陈小洪/卢志辉</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="32" customHeight="1">
+          <t>王小波/陈小洪</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="27" customHeight="1">
       <c r="A24" s="4" t="n">
         <v>7</v>
       </c>
@@ -1085,18 +1085,18 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>黄冬青/王小波</t>
+          <t>董广博/程建兴</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr"/>
       <c r="F24" s="4" t="inlineStr"/>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>陈顺星/罗琴荩</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="32" customHeight="1">
+          <t>黄冬青/张欣欣</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="27" customHeight="1">
       <c r="A25" s="4" t="n">
         <v>8</v>
       </c>
@@ -1107,23 +1107,23 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>混双</t>
+          <t>男双</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>陈顺星/滕菲</t>
+          <t>卢志辉/董广博</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr"/>
       <c r="F25" s="4" t="inlineStr"/>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>王小波/田茜</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="32" customHeight="1">
+          <t>刘继宇/苏大哲</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="27" customHeight="1">
       <c r="A26" s="4" t="n">
         <v>8</v>
       </c>
@@ -1139,18 +1139,18 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>刘继宇/卢志辉</t>
+          <t>陈小洪/罗琴荩</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr"/>
       <c r="F26" s="4" t="inlineStr"/>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>苏大哲/陈小洪</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="32" customHeight="1">
+          <t>陈财贵/王小波</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="27" customHeight="1">
       <c r="A27" s="4" t="n">
         <v>8</v>
       </c>
@@ -1161,19 +1161,19 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>男双</t>
+          <t>女双 (乱打)</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>罗蒙/罗琴荩</t>
+          <t>李祺祺/唐英武</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr"/>
       <c r="F27" s="4" t="inlineStr"/>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>林锋/黄冬青</t>
+          <t>黄冬青/程建兴</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1193,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1297,11 +1297,11 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>林锋</t>
+          <t>张欣欣</t>
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>5</v>
@@ -1310,7 +1310,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1320,54 +1320,54 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>罗琴荩</t>
+          <t>程建兴</t>
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>罗蒙</t>
+          <t>罗琴荩</t>
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D9" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1392,7 +1392,7 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>陈小洪</t>
+          <t>董广博</t>
         </is>
       </c>
       <c r="B11" s="7" t="n">
@@ -1411,26 +1411,26 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>陈顺星</t>
+          <t>陈小洪</t>
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>黄冬青</t>
+          <t>陈财贵</t>
         </is>
       </c>
       <c r="B13" s="7" t="n">
@@ -1449,26 +1449,26 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>崔倩男</t>
+          <t>黄冬青</t>
         </is>
       </c>
       <c r="B14" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C14" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="C14" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="D14" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>李祺祺</t>
+          <t>唐英武</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
@@ -1478,35 +1478,35 @@
         <v>0</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>滕菲</t>
+          <t>张燕红</t>
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C16" s="7" t="n">
         <v>0</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>田茜</t>
+          <t>李祺祺</t>
         </is>
       </c>
       <c r="B17" s="7" t="n">
@@ -1516,10 +1516,29 @@
         <v>0</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>滕菲</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
